--- a/artfynd/A 9530-2026 artfynd.xlsx
+++ b/artfynd/A 9530-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131452427</v>
       </c>
       <c r="B2" t="n">
-        <v>96612</v>
+        <v>96613</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>131450310</v>
       </c>
       <c r="B3" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>131452311</v>
       </c>
       <c r="B5" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 9530-2026 artfynd.xlsx
+++ b/artfynd/A 9530-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131452427</v>
       </c>
       <c r="B2" t="n">
-        <v>96613</v>
+        <v>96616</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>131450310</v>
       </c>
       <c r="B3" t="n">
-        <v>96506</v>
+        <v>96509</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>131450303</v>
       </c>
       <c r="B4" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>131452311</v>
       </c>
       <c r="B5" t="n">
-        <v>96506</v>
+        <v>96509</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 9530-2026 artfynd.xlsx
+++ b/artfynd/A 9530-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131452427</v>
       </c>
       <c r="B2" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>131450310</v>
       </c>
       <c r="B3" t="n">
-        <v>96509</v>
+        <v>96510</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>131450303</v>
       </c>
       <c r="B4" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>131452311</v>
       </c>
       <c r="B5" t="n">
-        <v>96509</v>
+        <v>96510</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 9530-2026 artfynd.xlsx
+++ b/artfynd/A 9530-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131452427</v>
+        <v>131450310</v>
       </c>
       <c r="B2" t="n">
-        <v>96642</v>
+        <v>96601</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>2170</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,17 +710,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gransjön , Srm</t>
+          <t>Gransjön, Gransjön, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593616</v>
+        <v>593587</v>
       </c>
       <c r="R2" t="n">
-        <v>6556232</v>
+        <v>6556166</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,9 +747,19 @@
           <t>2026-03-05</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -761,30 +771,25 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Göran Ekström</t>
+          <t>Göran Ekström, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131450310</v>
+        <v>131452311</v>
       </c>
       <c r="B3" t="n">
-        <v>96535</v>
+        <v>96601</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,17 +821,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gransjön, Gransjön, Srm</t>
+          <t>Gransjön , Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593587</v>
+        <v>593569</v>
       </c>
       <c r="R3" t="n">
-        <v>6556166</v>
+        <v>6556293</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -853,19 +858,9 @@
           <t>2026-03-05</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:03</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,25 +872,30 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Rolf Olsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Göran Ekström, Rolf Olsson</t>
+          <t>Rolf Olsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131450303</v>
+        <v>131452427</v>
       </c>
       <c r="B4" t="n">
-        <v>57100</v>
+        <v>96708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,45 +903,41 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gransjön, Gransjön, Srm</t>
+          <t>Gransjön , Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593498</v>
+        <v>593616</v>
       </c>
       <c r="R4" t="n">
-        <v>6556351</v>
+        <v>6556232</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -968,24 +964,9 @@
           <t>2026-03-05</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:51</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>10:51</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -997,25 +978,30 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Rolf Olsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Göran Ekström, Rolf Olsson</t>
+          <t>Rolf Olsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131452311</v>
+        <v>131450303</v>
       </c>
       <c r="B5" t="n">
-        <v>96535</v>
+        <v>57141</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1023,41 +1009,45 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2170</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gransjön , Srm</t>
+          <t>Gransjön, Gransjön, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593569</v>
+        <v>593498</v>
       </c>
       <c r="R5" t="n">
-        <v>6556293</v>
+        <v>6556351</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1084,9 +1074,24 @@
           <t>2026-03-05</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,20 +1103,15 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Göran Ekström</t>
+          <t>Göran Ekström, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 9530-2026 artfynd.xlsx
+++ b/artfynd/A 9530-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131450310</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131452311</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,6 +1010,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131452427</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1115,8 +1135,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131450303</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>